--- a/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="824">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
@@ -1099,10 +1099,10 @@
     <t xml:space="preserve">negotiation_darkness5</t>
   </si>
   <si>
-    <t xml:space="preserve">|You have finished your business in the Village of Atonement. Let's wait for Kettle to return. (To be continued)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|贖罪の村での用事を終えた。ケトルの帰りを待とう。（続く）</t>
+    <t xml:space="preserve">|You have finished your business in the Village of Atonement. Let's wait for Kettle to return.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|贖罪の村での用事を終えた。ケトルの帰りを待とう。</t>
   </si>
   <si>
     <t xml:space="preserve">demitas_spellwriter</t>
@@ -1917,6 +1917,21 @@
     <t xml:space="preserve">クラフト素材のトラック。</t>
   </si>
   <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedding Ceremony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結婚式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I love you. Let’s cerebrate with an unforgettable wedding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好き{だ}。素晴らしい式をあげる{のだ}。</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -1995,7 +2010,7 @@
     <t xml:space="preserve">EA 23.200</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.268</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.74</t>
@@ -2026,6 +2041,9 @@
   </si>
   <si>
     <t xml:space="preserve">EA 23.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.278</t>
   </si>
   <si>
     <t xml:space="preserve">主线任务</t>
@@ -2329,6 +2347,9 @@
     <t xml:space="preserve">制造小帮手</t>
   </si>
   <si>
+    <t xml:space="preserve">婚礼</t>
+  </si>
+  <si>
     <t xml:space="preserve">在长途跋涉之后，你终于到达了北提里斯。你还不知道在这片新天地之中有什么在等待着你。目前就把开始新生活并维持生计作为目标吧。</t>
   </si>
   <si>
@@ -2558,7 +2579,7 @@
     <t xml:space="preserve">|完成了比切林的委托。需回到赎罪村向比切林报告。</t>
   </si>
   <si>
-    <t xml:space="preserve">|赎罪村的事已经办完了。接下来等待凯特尔归来吧。(待续)</t>
+    <t xml:space="preserve">|赎罪村的事已经办完了。接下来等待凯特尔归来吧。</t>
   </si>
   <si>
     <t xml:space="preserve">汝是否略懂些魔法？</t>
@@ -2726,6 +2747,9 @@
   </si>
   <si>
     <t xml:space="preserve">追踪制造用的材料。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我爱你{。}。让我们举办最棒的婚礼吧{。}。</t>
   </si>
   <si>
     <t xml:space="preserve">嗯，看起来没什么问题呢。看你一副疲劳的样子，不如快喝喝看？这里是说好的奖励。</t>
@@ -2864,10 +2888,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -2876,7 +2900,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -2894,7 +2918,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -2906,7 +2930,7 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -2924,12 +2948,12 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2947,10 +2971,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C6" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -2959,7 +2983,7 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -2977,10 +3001,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C7" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -2989,7 +3013,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="G7" t="s">
         <v>36</v>
@@ -3007,12 +3031,12 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="G8" t="s">
         <v>39</v>
@@ -3030,10 +3054,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C9" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -3042,7 +3066,7 @@
         <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
@@ -3060,12 +3084,12 @@
         <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="G10" t="s">
         <v>47</v>
@@ -3083,12 +3107,12 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="G11" t="s">
         <v>50</v>
@@ -3106,10 +3130,10 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C12" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -3118,7 +3142,7 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="G12" t="s">
         <v>55</v>
@@ -3136,12 +3160,12 @@
         <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
@@ -3159,10 +3183,10 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C14" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -3171,7 +3195,7 @@
         <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="G14" t="s">
         <v>63</v>
@@ -3182,7 +3206,7 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="M14" t="s">
         <v>65</v>
@@ -3196,10 +3220,10 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C15" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -3208,7 +3232,7 @@
         <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="G15" t="s">
         <v>70</v>
@@ -3233,10 +3257,10 @@
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C16" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -3245,7 +3269,7 @@
         <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="G16" t="s">
         <v>77</v>
@@ -3263,10 +3287,10 @@
         <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C17" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D17" t="s">
         <v>80</v>
@@ -3275,7 +3299,7 @@
         <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="G17" t="s">
         <v>82</v>
@@ -3293,10 +3317,10 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C18" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D18" t="s">
         <v>85</v>
@@ -3305,7 +3329,7 @@
         <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="G18" t="s">
         <v>87</v>
@@ -3323,10 +3347,10 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C19" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D19" t="s">
         <v>90</v>
@@ -3335,7 +3359,7 @@
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="G19"/>
       <c r="H19" t="s">
@@ -3351,12 +3375,12 @@
         <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="G20"/>
       <c r="H20" t="s">
@@ -3372,7 +3396,7 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -3388,10 +3412,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C22" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -3400,7 +3424,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -3418,7 +3442,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -3434,10 +3458,10 @@
         <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C24" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D24" t="s">
         <v>103</v>
@@ -3446,7 +3470,7 @@
         <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G24" t="s">
         <v>105</v>
@@ -3464,12 +3488,12 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="G25" t="s">
         <v>108</v>
@@ -3487,12 +3511,12 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="G26" t="s">
         <v>111</v>
@@ -3510,7 +3534,7 @@
         <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -3526,10 +3550,10 @@
         <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C28" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D28" t="s">
         <v>115</v>
@@ -3538,7 +3562,7 @@
         <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="G28" t="s">
         <v>117</v>
@@ -3556,7 +3580,7 @@
         <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -3572,10 +3596,10 @@
         <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C30" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -3584,7 +3608,7 @@
         <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="G30" t="s">
         <v>82</v>
@@ -3602,10 +3626,10 @@
         <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C31" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D31" t="s">
         <v>125</v>
@@ -3614,7 +3638,7 @@
         <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="G31" t="s">
         <v>82</v>
@@ -3632,10 +3656,10 @@
         <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C32" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="D32" t="s">
         <v>128</v>
@@ -3644,7 +3668,7 @@
         <v>129</v>
       </c>
       <c r="F32" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="G32" t="s">
         <v>130</v>
@@ -3662,12 +3686,12 @@
         <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D33"/>
       <c r="E33"/>
       <c r="F33" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="G33" t="s">
         <v>133</v>
@@ -3685,7 +3709,7 @@
         <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D34"/>
       <c r="E34"/>
@@ -3701,10 +3725,10 @@
         <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C35" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D35" t="s">
         <v>137</v>
@@ -3713,7 +3737,7 @@
         <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="G35" t="s">
         <v>139</v>
@@ -3731,12 +3755,12 @@
         <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="G36" t="s">
         <v>142</v>
@@ -3754,12 +3778,12 @@
         <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="G37" t="s">
         <v>145</v>
@@ -3777,7 +3801,7 @@
         <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D38"/>
       <c r="E38"/>
@@ -3793,10 +3817,10 @@
         <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C39" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D39" t="s">
         <v>149</v>
@@ -3805,7 +3829,7 @@
         <v>150</v>
       </c>
       <c r="F39" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="G39" t="s">
         <v>151</v>
@@ -3823,12 +3847,12 @@
         <v>153</v>
       </c>
       <c r="B40" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="G40" t="s">
         <v>154</v>
@@ -3846,7 +3870,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D41"/>
       <c r="E41"/>
@@ -3862,10 +3886,10 @@
         <v>157</v>
       </c>
       <c r="B42" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C42" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D42" t="s">
         <v>158</v>
@@ -3874,7 +3898,7 @@
         <v>159</v>
       </c>
       <c r="F42" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="G42" t="s">
         <v>160</v>
@@ -3892,7 +3916,7 @@
         <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D43"/>
       <c r="E43"/>
@@ -3908,10 +3932,10 @@
         <v>163</v>
       </c>
       <c r="B44" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C44" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D44" t="s">
         <v>164</v>
@@ -3920,7 +3944,7 @@
         <v>165</v>
       </c>
       <c r="F44" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="G44" t="s">
         <v>166</v>
@@ -3938,12 +3962,12 @@
         <v>168</v>
       </c>
       <c r="B45" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="G45" t="s">
         <v>169</v>
@@ -3961,12 +3985,12 @@
         <v>171</v>
       </c>
       <c r="B46" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
       <c r="F46" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="G46" t="s">
         <v>172</v>
@@ -3984,12 +4008,12 @@
         <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="G47" t="s">
         <v>175</v>
@@ -4007,12 +4031,12 @@
         <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="G48" t="s">
         <v>175</v>
@@ -4030,12 +4054,12 @@
         <v>178</v>
       </c>
       <c r="B49" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="G49" t="s">
         <v>179</v>
@@ -4053,7 +4077,7 @@
         <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D50"/>
       <c r="E50"/>
@@ -4069,10 +4093,10 @@
         <v>182</v>
       </c>
       <c r="B51" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C51" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -4081,7 +4105,7 @@
         <v>184</v>
       </c>
       <c r="F51" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="G51" t="s">
         <v>185</v>
@@ -4099,10 +4123,10 @@
         <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C52" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D52" t="s">
         <v>188</v>
@@ -4111,7 +4135,7 @@
         <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="G52" t="s">
         <v>190</v>
@@ -4129,7 +4153,7 @@
         <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D53"/>
       <c r="E53"/>
@@ -4145,10 +4169,10 @@
         <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C54" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D54" t="s">
         <v>194</v>
@@ -4157,7 +4181,7 @@
         <v>195</v>
       </c>
       <c r="F54" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="G54" t="s">
         <v>196</v>
@@ -4175,7 +4199,7 @@
         <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D55"/>
       <c r="E55"/>
@@ -4191,10 +4215,10 @@
         <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C56" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D56" t="s">
         <v>200</v>
@@ -4203,7 +4227,7 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="G56" t="s">
         <v>202</v>
@@ -4221,10 +4245,10 @@
         <v>204</v>
       </c>
       <c r="B57" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C57" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D57" t="s">
         <v>205</v>
@@ -4233,7 +4257,7 @@
         <v>206</v>
       </c>
       <c r="F57" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="G57" t="s">
         <v>207</v>
@@ -4251,10 +4275,10 @@
         <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C58" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D58" t="s">
         <v>210</v>
@@ -4263,7 +4287,7 @@
         <v>211</v>
       </c>
       <c r="F58" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="G58" t="s">
         <v>212</v>
@@ -4281,10 +4305,10 @@
         <v>214</v>
       </c>
       <c r="B59" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C59" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D59" t="s">
         <v>215</v>
@@ -4293,7 +4317,7 @@
         <v>216</v>
       </c>
       <c r="F59" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="G59" t="s">
         <v>217</v>
@@ -4311,10 +4335,10 @@
         <v>219</v>
       </c>
       <c r="B60" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C60" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="D60" t="s">
         <v>220</v>
@@ -4323,7 +4347,7 @@
         <v>221</v>
       </c>
       <c r="F60" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="G60" t="s">
         <v>222</v>
@@ -4341,10 +4365,10 @@
         <v>224</v>
       </c>
       <c r="B61" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C61" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="D61" t="s">
         <v>225</v>
@@ -4353,7 +4377,7 @@
         <v>226</v>
       </c>
       <c r="F61" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="G61" t="s">
         <v>227</v>
@@ -4371,10 +4395,10 @@
         <v>229</v>
       </c>
       <c r="B62" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C62" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D62" t="s">
         <v>230</v>
@@ -4383,7 +4407,7 @@
         <v>231</v>
       </c>
       <c r="F62" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="G62" t="s">
         <v>232</v>
@@ -4401,10 +4425,10 @@
         <v>234</v>
       </c>
       <c r="B63" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C63" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D63" t="s">
         <v>235</v>
@@ -4413,7 +4437,7 @@
         <v>236</v>
       </c>
       <c r="F63" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="G63" t="s">
         <v>237</v>
@@ -4431,12 +4455,12 @@
         <v>239</v>
       </c>
       <c r="B64" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D64"/>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="G64" t="s">
         <v>240</v>
@@ -4454,12 +4478,12 @@
         <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D65"/>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G65" t="s">
         <v>243</v>
@@ -4477,12 +4501,12 @@
         <v>245</v>
       </c>
       <c r="B66" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D66"/>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="G66" t="s">
         <v>246</v>
@@ -4500,12 +4524,12 @@
         <v>248</v>
       </c>
       <c r="B67" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D67"/>
       <c r="E67"/>
       <c r="F67" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="G67" t="s">
         <v>249</v>
@@ -4523,12 +4547,12 @@
         <v>251</v>
       </c>
       <c r="B68" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="G68" t="s">
         <v>252</v>
@@ -4546,12 +4570,12 @@
         <v>254</v>
       </c>
       <c r="B69" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D69"/>
       <c r="E69"/>
       <c r="F69" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="G69" t="s">
         <v>255</v>
@@ -4569,12 +4593,12 @@
         <v>257</v>
       </c>
       <c r="B70" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D70"/>
       <c r="E70"/>
       <c r="F70" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="G70" t="s">
         <v>258</v>
@@ -4592,12 +4616,12 @@
         <v>260</v>
       </c>
       <c r="B71" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="G71" t="s">
         <v>261</v>
@@ -4615,12 +4639,12 @@
         <v>263</v>
       </c>
       <c r="B72" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="G72" t="s">
         <v>264</v>
@@ -4638,7 +4662,7 @@
         <v>266</v>
       </c>
       <c r="B73" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D73"/>
       <c r="E73"/>
@@ -4656,7 +4680,7 @@
         <v>268</v>
       </c>
       <c r="B74" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D74"/>
       <c r="E74"/>
@@ -4674,10 +4698,10 @@
         <v>269</v>
       </c>
       <c r="B75" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C75" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D75" t="s">
         <v>270</v>
@@ -4686,7 +4710,7 @@
         <v>271</v>
       </c>
       <c r="F75" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="G75" t="s">
         <v>272</v>
@@ -4704,10 +4728,10 @@
         <v>274</v>
       </c>
       <c r="B76" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C76" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D76" t="s">
         <v>275</v>
@@ -4716,7 +4740,7 @@
         <v>276</v>
       </c>
       <c r="F76" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G76" t="s">
         <v>277</v>
@@ -4734,10 +4758,10 @@
         <v>279</v>
       </c>
       <c r="B77" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C77" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D77" t="s">
         <v>280</v>
@@ -4746,7 +4770,7 @@
         <v>281</v>
       </c>
       <c r="F77" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="G77" t="s">
         <v>282</v>
@@ -4764,10 +4788,10 @@
         <v>284</v>
       </c>
       <c r="B78" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C78" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D78" t="s">
         <v>285</v>
@@ -4776,7 +4800,7 @@
         <v>286</v>
       </c>
       <c r="F78" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="G78" t="s">
         <v>287</v>
@@ -4794,10 +4818,10 @@
         <v>289</v>
       </c>
       <c r="B79" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C79" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D79" t="s">
         <v>290</v>
@@ -4806,7 +4830,7 @@
         <v>291</v>
       </c>
       <c r="F79" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="G79" t="s">
         <v>292</v>
@@ -4824,7 +4848,7 @@
         <v>294</v>
       </c>
       <c r="B80" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D80"/>
       <c r="E80"/>
@@ -4845,10 +4869,10 @@
         <v>296</v>
       </c>
       <c r="B81" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C81" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D81" t="s">
         <v>297</v>
@@ -4857,7 +4881,7 @@
         <v>298</v>
       </c>
       <c r="F81" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G81" t="s">
         <v>299</v>
@@ -4875,10 +4899,10 @@
         <v>301</v>
       </c>
       <c r="B82" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C82" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D82" t="s">
         <v>302</v>
@@ -4887,7 +4911,7 @@
         <v>303</v>
       </c>
       <c r="F82" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="G82" t="s">
         <v>304</v>
@@ -4905,10 +4929,10 @@
         <v>306</v>
       </c>
       <c r="B83" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C83" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D83" t="s">
         <v>307</v>
@@ -4917,7 +4941,7 @@
         <v>308</v>
       </c>
       <c r="F83" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="G83" t="s">
         <v>309</v>
@@ -4935,10 +4959,10 @@
         <v>311</v>
       </c>
       <c r="B84" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C84" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D84" t="s">
         <v>312</v>
@@ -4947,7 +4971,7 @@
         <v>313</v>
       </c>
       <c r="F84" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="G84" t="s">
         <v>232</v>
@@ -4965,10 +4989,10 @@
         <v>314</v>
       </c>
       <c r="B85" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C85" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D85" t="s">
         <v>315</v>
@@ -4977,7 +5001,7 @@
         <v>316</v>
       </c>
       <c r="F85" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="G85" t="s">
         <v>317</v>
@@ -4995,10 +5019,10 @@
         <v>319</v>
       </c>
       <c r="B86" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C86" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D86" t="s">
         <v>320</v>
@@ -5007,7 +5031,7 @@
         <v>321</v>
       </c>
       <c r="F86" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="G86" t="s">
         <v>322</v>
@@ -5025,12 +5049,12 @@
         <v>324</v>
       </c>
       <c r="B87" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="G87" t="s">
         <v>325</v>
@@ -5048,12 +5072,12 @@
         <v>327</v>
       </c>
       <c r="B88" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="G88" t="s">
         <v>325</v>
@@ -5071,12 +5095,12 @@
         <v>328</v>
       </c>
       <c r="B89" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="G89" t="s">
         <v>325</v>
@@ -5094,12 +5118,12 @@
         <v>329</v>
       </c>
       <c r="B90" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="G90" t="s">
         <v>330</v>
@@ -5117,12 +5141,12 @@
         <v>332</v>
       </c>
       <c r="B91" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D91"/>
       <c r="E91"/>
       <c r="F91" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="G91" t="s">
         <v>333</v>
@@ -5140,12 +5164,12 @@
         <v>335</v>
       </c>
       <c r="B92" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="G92" t="s">
         <v>336</v>
@@ -5163,12 +5187,12 @@
         <v>338</v>
       </c>
       <c r="B93" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="G93" t="s">
         <v>339</v>
@@ -5186,10 +5210,10 @@
         <v>341</v>
       </c>
       <c r="B94" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C94" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="D94" t="s">
         <v>342</v>
@@ -5198,7 +5222,7 @@
         <v>343</v>
       </c>
       <c r="F94" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="G94" t="s">
         <v>344</v>
@@ -5216,12 +5240,12 @@
         <v>346</v>
       </c>
       <c r="B95" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="G95" t="s">
         <v>347</v>
@@ -5239,12 +5263,12 @@
         <v>349</v>
       </c>
       <c r="B96" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="G96" t="s">
         <v>350</v>
@@ -5262,12 +5286,12 @@
         <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D97"/>
       <c r="E97"/>
       <c r="F97" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="G97" t="s">
         <v>353</v>
@@ -5285,12 +5309,12 @@
         <v>355</v>
       </c>
       <c r="B98" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D98"/>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="G98" t="s">
         <v>356</v>
@@ -5308,12 +5332,12 @@
         <v>358</v>
       </c>
       <c r="B99" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D99"/>
       <c r="E99"/>
       <c r="F99" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="G99" t="s">
         <v>359</v>
@@ -5331,10 +5355,10 @@
         <v>361</v>
       </c>
       <c r="B100" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C100" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D100" t="s">
         <v>362</v>
@@ -5343,7 +5367,7 @@
         <v>363</v>
       </c>
       <c r="F100" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="G100" t="s">
         <v>364</v>
@@ -5361,10 +5385,10 @@
         <v>366</v>
       </c>
       <c r="B101" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C101" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D101" t="s">
         <v>367</v>
@@ -5373,7 +5397,7 @@
         <v>368</v>
       </c>
       <c r="F101" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G101" t="s">
         <v>277</v>
@@ -5391,10 +5415,10 @@
         <v>369</v>
       </c>
       <c r="B102" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C102" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D102" t="s">
         <v>367</v>
@@ -5403,7 +5427,7 @@
         <v>368</v>
       </c>
       <c r="F102" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G102" t="s">
         <v>277</v>
@@ -5421,10 +5445,10 @@
         <v>370</v>
       </c>
       <c r="B103" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C103" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D103" t="s">
         <v>371</v>
@@ -5433,7 +5457,7 @@
         <v>372</v>
       </c>
       <c r="F103" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="G103"/>
       <c r="H103" t="s">
@@ -5449,10 +5473,10 @@
         <v>374</v>
       </c>
       <c r="B104" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C104" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D104" t="s">
         <v>375</v>
@@ -5461,7 +5485,7 @@
         <v>376</v>
       </c>
       <c r="F104" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G104" t="s">
         <v>277</v>
@@ -5479,10 +5503,10 @@
         <v>377</v>
       </c>
       <c r="B105" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C105" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D105" t="s">
         <v>378</v>
@@ -5509,10 +5533,10 @@
         <v>381</v>
       </c>
       <c r="B106" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C106" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D106" t="s">
         <v>382</v>
@@ -5539,10 +5563,10 @@
         <v>384</v>
       </c>
       <c r="B107" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C107" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D107" t="s">
         <v>385</v>
@@ -5569,10 +5593,10 @@
         <v>387</v>
       </c>
       <c r="B108" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C108" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D108" t="s">
         <v>388</v>
@@ -5599,10 +5623,10 @@
         <v>390</v>
       </c>
       <c r="B109" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C109" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D109" t="s">
         <v>391</v>
@@ -5611,7 +5635,7 @@
         <v>392</v>
       </c>
       <c r="F109" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="G109" t="s">
         <v>393</v>
@@ -5629,12 +5653,12 @@
         <v>395</v>
       </c>
       <c r="B110" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D110"/>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G110" t="s">
         <v>396</v>
@@ -5652,10 +5676,10 @@
         <v>398</v>
       </c>
       <c r="B111" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C111" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D111" t="s">
         <v>399</v>
@@ -5664,7 +5688,7 @@
         <v>400</v>
       </c>
       <c r="F111" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="G111" t="s">
         <v>401</v>
@@ -5682,10 +5706,10 @@
         <v>403</v>
       </c>
       <c r="B112" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C112" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D112" t="s">
         <v>404</v>
@@ -5694,7 +5718,7 @@
         <v>405</v>
       </c>
       <c r="F112" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="G112" t="s">
         <v>406</v>
@@ -5712,12 +5736,12 @@
         <v>408</v>
       </c>
       <c r="B113" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D113"/>
       <c r="E113"/>
       <c r="F113" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="G113" t="s">
         <v>409</v>
@@ -5735,10 +5759,10 @@
         <v>411</v>
       </c>
       <c r="B114" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C114" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D114" t="s">
         <v>412</v>
@@ -5747,7 +5771,7 @@
         <v>413</v>
       </c>
       <c r="F114" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="G114" t="s">
         <v>414</v>
@@ -5765,10 +5789,10 @@
         <v>416</v>
       </c>
       <c r="B115" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C115" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D115" t="s">
         <v>417</v>
@@ -5777,7 +5801,7 @@
         <v>418</v>
       </c>
       <c r="F115" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="G115" t="s">
         <v>419</v>
@@ -5795,12 +5819,12 @@
         <v>421</v>
       </c>
       <c r="B116" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D116"/>
       <c r="E116"/>
       <c r="F116" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="G116" t="s">
         <v>422</v>
@@ -5818,10 +5842,10 @@
         <v>424</v>
       </c>
       <c r="B117" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C117" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D117" t="s">
         <v>425</v>
@@ -5830,7 +5854,7 @@
         <v>426</v>
       </c>
       <c r="F117" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="G117" t="s">
         <v>427</v>
@@ -5848,10 +5872,10 @@
         <v>429</v>
       </c>
       <c r="B118" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C118" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D118" t="s">
         <v>430</v>
@@ -5860,7 +5884,7 @@
         <v>431</v>
       </c>
       <c r="F118" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="G118" t="s">
         <v>432</v>
@@ -5878,12 +5902,12 @@
         <v>434</v>
       </c>
       <c r="B119" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D119"/>
       <c r="E119"/>
       <c r="F119" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="G119" t="s">
         <v>435</v>
@@ -5901,10 +5925,10 @@
         <v>437</v>
       </c>
       <c r="B120" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C120" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="D120" t="s">
         <v>438</v>
@@ -5913,7 +5937,7 @@
         <v>439</v>
       </c>
       <c r="F120" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="G120" t="s">
         <v>440</v>
@@ -5931,10 +5955,10 @@
         <v>442</v>
       </c>
       <c r="B121" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C121" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D121" t="s">
         <v>443</v>
@@ -5943,7 +5967,7 @@
         <v>444</v>
       </c>
       <c r="F121" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="G121" t="s">
         <v>445</v>
@@ -5961,10 +5985,10 @@
         <v>447</v>
       </c>
       <c r="B122" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C122" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="D122" t="s">
         <v>448</v>
@@ -5973,7 +5997,7 @@
         <v>449</v>
       </c>
       <c r="F122" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G122" t="s">
         <v>450</v>
@@ -5991,10 +6015,10 @@
         <v>452</v>
       </c>
       <c r="B123" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C123" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D123" t="s">
         <v>453</v>
@@ -6003,7 +6027,7 @@
         <v>454</v>
       </c>
       <c r="F123" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="G123" t="s">
         <v>455</v>
@@ -6021,10 +6045,10 @@
         <v>457</v>
       </c>
       <c r="B124" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C124" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D124" t="s">
         <v>458</v>
@@ -6033,7 +6057,7 @@
         <v>459</v>
       </c>
       <c r="F124" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="G124" t="s">
         <v>460</v>
@@ -6051,10 +6075,10 @@
         <v>462</v>
       </c>
       <c r="B125" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C125" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D125" t="s">
         <v>463</v>
@@ -6063,7 +6087,7 @@
         <v>464</v>
       </c>
       <c r="F125" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="G125" t="s">
         <v>465</v>
@@ -6081,10 +6105,10 @@
         <v>467</v>
       </c>
       <c r="B126" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C126" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D126" t="s">
         <v>468</v>
@@ -6093,7 +6117,7 @@
         <v>469</v>
       </c>
       <c r="F126" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="G126" t="s">
         <v>470</v>
@@ -6111,10 +6135,10 @@
         <v>472</v>
       </c>
       <c r="B127" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C127" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D127" t="s">
         <v>473</v>
@@ -6123,7 +6147,7 @@
         <v>474</v>
       </c>
       <c r="F127" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="G127" t="s">
         <v>475</v>
@@ -6141,10 +6165,10 @@
         <v>477</v>
       </c>
       <c r="B128" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C128" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D128" t="s">
         <v>478</v>
@@ -6153,7 +6177,7 @@
         <v>479</v>
       </c>
       <c r="F128" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="G128" t="s">
         <v>480</v>
@@ -6171,10 +6195,10 @@
         <v>482</v>
       </c>
       <c r="B129" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C129" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D129" t="s">
         <v>483</v>
@@ -6183,7 +6207,7 @@
         <v>484</v>
       </c>
       <c r="F129" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="G129" t="s">
         <v>485</v>
@@ -6201,10 +6225,10 @@
         <v>487</v>
       </c>
       <c r="B130" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C130" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="D130" t="s">
         <v>488</v>
@@ -6213,7 +6237,7 @@
         <v>489</v>
       </c>
       <c r="F130" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="G130" t="s">
         <v>490</v>
@@ -6231,10 +6255,10 @@
         <v>492</v>
       </c>
       <c r="B131" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C131" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D131" t="s">
         <v>493</v>
@@ -6243,7 +6267,7 @@
         <v>494</v>
       </c>
       <c r="F131" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="G131" t="s">
         <v>495</v>
@@ -6261,10 +6285,10 @@
         <v>497</v>
       </c>
       <c r="B132" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C132" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D132" t="s">
         <v>498</v>
@@ -6273,7 +6297,7 @@
         <v>499</v>
       </c>
       <c r="F132" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="G132" t="s">
         <v>500</v>
@@ -6291,10 +6315,10 @@
         <v>502</v>
       </c>
       <c r="B133" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C133" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="D133" t="s">
         <v>503</v>
@@ -6303,7 +6327,7 @@
         <v>504</v>
       </c>
       <c r="F133" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="G133" t="s">
         <v>505</v>
@@ -6321,10 +6345,10 @@
         <v>507</v>
       </c>
       <c r="B134" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C134" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D134" t="s">
         <v>508</v>
@@ -6333,7 +6357,7 @@
         <v>509</v>
       </c>
       <c r="F134" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="G134" t="s">
         <v>510</v>
@@ -6351,10 +6375,10 @@
         <v>512</v>
       </c>
       <c r="B135" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C135" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D135" t="s">
         <v>513</v>
@@ -6363,7 +6387,7 @@
         <v>514</v>
       </c>
       <c r="F135" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="G135" t="s">
         <v>515</v>
@@ -6381,10 +6405,10 @@
         <v>517</v>
       </c>
       <c r="B136" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C136" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D136" t="s">
         <v>518</v>
@@ -6393,7 +6417,7 @@
         <v>519</v>
       </c>
       <c r="F136" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="G136" t="s">
         <v>520</v>
@@ -6411,10 +6435,10 @@
         <v>522</v>
       </c>
       <c r="B137" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C137" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="D137" t="s">
         <v>523</v>
@@ -6423,7 +6447,7 @@
         <v>524</v>
       </c>
       <c r="F137" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="G137" t="s">
         <v>525</v>
@@ -6441,10 +6465,10 @@
         <v>527</v>
       </c>
       <c r="B138" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C138" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D138" t="s">
         <v>528</v>
@@ -6453,7 +6477,7 @@
         <v>529</v>
       </c>
       <c r="F138" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="G138" t="s">
         <v>530</v>
@@ -6471,10 +6495,10 @@
         <v>532</v>
       </c>
       <c r="B139" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C139" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D139" t="s">
         <v>528</v>
@@ -6483,7 +6507,7 @@
         <v>529</v>
       </c>
       <c r="F139" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="G139" t="s">
         <v>530</v>
@@ -6501,10 +6525,10 @@
         <v>534</v>
       </c>
       <c r="B140" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C140" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D140" t="s">
         <v>535</v>
@@ -6513,7 +6537,7 @@
         <v>536</v>
       </c>
       <c r="F140" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="G140" t="s">
         <v>537</v>
@@ -6531,10 +6555,10 @@
         <v>539</v>
       </c>
       <c r="B141" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C141" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="D141" t="s">
         <v>540</v>
@@ -6543,7 +6567,7 @@
         <v>541</v>
       </c>
       <c r="F141" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="G141" t="s">
         <v>542</v>
@@ -6561,10 +6585,10 @@
         <v>544</v>
       </c>
       <c r="B142" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C142" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D142" t="s">
         <v>545</v>
@@ -6573,7 +6597,7 @@
         <v>546</v>
       </c>
       <c r="F142" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="G142" t="s">
         <v>547</v>
@@ -6591,10 +6615,10 @@
         <v>549</v>
       </c>
       <c r="B143" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C143" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D143" t="s">
         <v>550</v>
@@ -6603,7 +6627,7 @@
         <v>551</v>
       </c>
       <c r="F143" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="G143" t="s">
         <v>552</v>
@@ -6621,10 +6645,10 @@
         <v>554</v>
       </c>
       <c r="B144" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C144" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D144" t="s">
         <v>555</v>
@@ -6633,7 +6657,7 @@
         <v>556</v>
       </c>
       <c r="F144" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="G144" t="s">
         <v>557</v>
@@ -6651,10 +6675,10 @@
         <v>559</v>
       </c>
       <c r="B145" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C145" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="D145" t="s">
         <v>560</v>
@@ -6663,7 +6687,7 @@
         <v>561</v>
       </c>
       <c r="F145" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="G145" t="s">
         <v>562</v>
@@ -6681,10 +6705,10 @@
         <v>564</v>
       </c>
       <c r="B146" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C146" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="D146" t="s">
         <v>565</v>
@@ -6693,7 +6717,7 @@
         <v>566</v>
       </c>
       <c r="F146" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="G146" t="s">
         <v>567</v>
@@ -6711,10 +6735,10 @@
         <v>569</v>
       </c>
       <c r="B147" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C147" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
@@ -6723,7 +6747,7 @@
         <v>571</v>
       </c>
       <c r="F147" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="G147" t="s">
         <v>572</v>
@@ -6735,6 +6759,36 @@
       <c r="K147"/>
       <c r="M147"/>
       <c r="N147"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>574</v>
+      </c>
+      <c r="B148" t="s">
+        <v>616</v>
+      </c>
+      <c r="C148" t="s">
+        <v>703</v>
+      </c>
+      <c r="D148" t="s">
+        <v>575</v>
+      </c>
+      <c r="E148" t="s">
+        <v>576</v>
+      </c>
+      <c r="F148" t="s">
+        <v>822</v>
+      </c>
+      <c r="G148" t="s">
+        <v>577</v>
+      </c>
+      <c r="H148" t="s">
+        <v>578</v>
+      </c>
+      <c r="J148"/>
+      <c r="K148"/>
+      <c r="M148"/>
+      <c r="N148"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:N2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
@@ -778,10 +778,10 @@
     <t xml:space="preserve">vernis_gold5</t>
   </si>
   <si>
-    <t xml:space="preserve">The development of Vernis has begun. Grow the Hearth Stone in Vernis and report it to Loytel. Ask Loytel if you're unsure how to grow the Hearth Stone. Also, you need to continue conversations with your companions on the quest board. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ヴェルニースの開拓が始まった。ヴェルニースの盟約の石を成長させ、ロイテルに報告しなければならない。石の成長の方法がわからない場合は、ロイテルに相談しよう。また、依頼掲示板でクルイツゥア達との会話を進行させる必要がある。</t>
+    <t xml:space="preserve">The development of Vernis has begun. Grow the Hearth Stone in Vernis and report it to Loytel. Ask Loytel if you're unsure how to grow the Hearth Stone. Before reporting, you must progress your conversation events with your companions through the Quest Board.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヴェルニースの開拓が始まった。ヴェルニースの盟約の石を成長させ、ロイテルに報告しなければならない。石の成長の方法がわからない場合は、ロイテルに相談しよう。報告の前に、依頼掲示板からクルイツゥア達との会話を進行させておく必要がある。</t>
   </si>
   <si>
     <t xml:space="preserve">vernis_gold6</t>
@@ -1974,7 +1974,7 @@
     <t xml:space="preserve">EA 23.12 fix 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta 22.83</t>
+    <t xml:space="preserve">EA 23.283</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.100</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">罗伊特尔给了你「土地产权证」。获得韦尔尼斯的产权之后，就向罗伊特尔报告吧。</t>
   </si>
   <si>
-    <t xml:space="preserve">韦尔尼斯的开拓开始了。在韦尔尼斯盟约之石的等级成长后，再向罗伊特尔报告吧。如果不明白让盟约之石成长的方法，可以去找罗伊特尔聊聊。另外，需要通过委托告示板和库罗茨亚他们推进对话剧情。</t>
+    <t xml:space="preserve">韦尔尼斯的开拓开始了。在韦尔尼斯盟约之石的等级成长后，再向罗伊特尔报告吧。如果不明白让盟约之石成长的方法，可以去找罗伊特尔聊聊。在报告之前，必须先通过委托告示板和库罗茨亚他们推进对话剧情。</t>
   </si>
   <si>
     <t xml:space="preserve">韦尔尼斯地下出现了龙。做好消灭龙的心理准备就和罗伊特尔说话吧。</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
